--- a/fundraising_order_forms/014_custom_coupon_booklet_order_form--fundraising_order_forms.xlsx
+++ b/fundraising_order_forms/014_custom_coupon_booklet_order_form--fundraising_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'booklet_1'}</t>
+          <t>booklet_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Booklet 1'}</t>
+          <t>Booklet 1</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'booklet_2'}</t>
+          <t>booklet_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Booklet 2'}</t>
+          <t>Booklet 2</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'booklet_3'}</t>
+          <t>booklet_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Booklet 3'}</t>
+          <t>Booklet 3</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'standard'}</t>
+          <t>standard</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Standard'}</t>
+          <t>Standard</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'express'}</t>
+          <t>express</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Express'}</t>
+          <t>Express</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'ups'}</t>
+          <t>ups</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'UPS'}</t>
+          <t>UPS</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'a3'}</t>
+          <t>a3</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'A3'}</t>
+          <t>A3</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'letter'}</t>
+          <t>letter</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Letter'}</t>
+          <t>Letter</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'legal'}</t>
+          <t>legal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Legal'}</t>
+          <t>Legal</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'tabloid'}</t>
+          <t>tabloid</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Tabloid'}</t>
+          <t>Tabloid</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'2-up'}</t>
+          <t>2-up</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '2-up'}</t>
+          <t>2-up</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'3-up'}</t>
+          <t>3-up</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '3-up'}</t>
+          <t>3-up</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'4-up'}</t>
+          <t>4-up</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '4-up'}</t>
+          <t>4-up</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'accept'}</t>
+          <t>accept</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Accept'}</t>
+          <t>Accept</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'decline'}</t>
+          <t>decline</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Decline'}</t>
+          <t>Decline</t>
         </is>
       </c>
     </row>
